--- a/MULTIPUNTO/6553 Datos Multipunto ZUCCHETTI SOFTWARE SPAIN.xlsx
+++ b/MULTIPUNTO/6553 Datos Multipunto ZUCCHETTI SOFTWARE SPAIN.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -49,9 +49,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,21 +418,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P17"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="19" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="21" customWidth="1" min="9" max="9"/>
-    <col width="21" customWidth="1" min="10" max="10"/>
-    <col width="21" customWidth="1" min="11" max="11"/>
-    <col width="21" customWidth="1" min="12" max="12"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="20" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
@@ -526,17 +527,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CE ENERGÍA, S.A.</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D2" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>46210</v>
+          <t>ELEIA</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -544,13 +545,13 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0.228378</v>
+        <v>0.2336061538805538</v>
       </c>
       <c r="H2" t="n">
-        <v>0.140409</v>
+        <v>0.1567067040888605</v>
       </c>
       <c r="I2" t="n">
-        <v>0.112008</v>
+        <v>0.129331082006255</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -584,17 +585,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CE ENERGÍA, S.A.</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D3" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46210</v>
+          <t>ELEIA</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -602,37 +603,37 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0.20376</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0.161756</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0.132449</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.107673</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0.088375</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>0.112552</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.647</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>3.0TD</t>
+          <t>2.0TD</t>
         </is>
       </c>
     </row>
@@ -645,14 +646,14 @@
           <t>ELEIA</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>46210</v>
+      <c r="C4" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -660,22 +661,22 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0.2336061538805538</v>
+        <v>0.2140865731236269</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1567067040888605</v>
+        <v>0.1776397511521125</v>
       </c>
       <c r="I4" t="n">
-        <v>0.129331082006255</v>
+        <v>0.1418357068521347</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.1227895988321102</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>0.105819034243189</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>0.1262996316783944</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -690,7 +691,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>2.0TD</t>
+          <t>3.0TD</t>
         </is>
       </c>
     </row>
@@ -703,14 +704,14 @@
           <t>ELEIA</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>46210</v>
+      <c r="C5" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -748,7 +749,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>2.0TD</t>
+          <t>3.0TD</t>
         </is>
       </c>
     </row>
@@ -758,17 +759,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ELEIA</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="n">
+          <t>ENERGYA VM</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="n">
         <v>46210</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>46210</v>
+      <c r="D6" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -776,22 +777,22 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0.2140865731236269</v>
+        <v>0.225418</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1776397511521125</v>
+        <v>0.144702</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1418357068521347</v>
+        <v>0.11562</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1227895988321102</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.105819034243189</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1262996316783944</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
@@ -806,7 +807,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>3.0TD</t>
+          <t>2.0TD</t>
         </is>
       </c>
     </row>
@@ -816,17 +817,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ELEIA</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="n">
+          <t>ENERGYA VM</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="n">
         <v>46210</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>46210</v>
+      <c r="D7" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -852,7 +853,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>1.647</v>
+        <v>3.1</v>
       </c>
       <c r="N7" t="n">
         <v>1.5</v>
@@ -864,7 +865,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>3.0TD</t>
+          <t>2.0TD</t>
         </is>
       </c>
     </row>
@@ -877,14 +878,14 @@
           <t>ENERGYA VM</t>
         </is>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>46210</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>46210</v>
+      <c r="D8" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -892,22 +893,22 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0.225418</v>
+        <v>0.186692</v>
       </c>
       <c r="H8" t="n">
-        <v>0.144702</v>
+        <v>0.156747</v>
       </c>
       <c r="I8" t="n">
-        <v>0.11562</v>
+        <v>0.130507</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.109694</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.09471400000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.110292</v>
       </c>
       <c r="M8" t="n">
         <v>0</v>
@@ -922,7 +923,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>2.0TD</t>
+          <t>3.0TD</t>
         </is>
       </c>
     </row>
@@ -935,14 +936,14 @@
           <t>ENERGYA VM</t>
         </is>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>46210</v>
       </c>
-      <c r="D9" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46210</v>
+      <c r="D9" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -950,32 +951,32 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0.186692</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>0.156747</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>0.130507</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.109694</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.09471400000000001</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0.110292</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -993,14 +994,14 @@
           <t>IBERDROLA</t>
         </is>
       </c>
-      <c r="C10" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>46210</v>
+      <c r="C10" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1051,14 +1052,14 @@
           <t>IBERDROLA</t>
         </is>
       </c>
-      <c r="C11" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>46210</v>
+      <c r="C11" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1109,14 +1110,14 @@
           <t>IBERDROLA</t>
         </is>
       </c>
-      <c r="C12" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>46210</v>
+      <c r="C12" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1167,14 +1168,14 @@
           <t>IBERDROLA</t>
         </is>
       </c>
-      <c r="C13" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>46210</v>
+      <c r="C13" s="2" t="n">
+        <v>46204</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1225,14 +1226,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C14" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>46210</v>
+      <c r="C14" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1283,14 +1284,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C15" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>46210</v>
+      <c r="C15" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1341,14 +1342,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C16" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>46210</v>
+      <c r="C16" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -1399,14 +1400,14 @@
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C17" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>46210</v>
+      <c r="C17" s="2" t="n">
+        <v>46209</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>46213</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1443,6 +1444,238 @@
         </is>
       </c>
       <c r="P17" t="inlineStr">
+        <is>
+          <t>3.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>6553</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>VISALIA</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>0.228378</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.140409</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.112008</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>6553</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>VISALIA</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>46210</v>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>0.20376</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.161756</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.132449</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.107673</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.088375</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.112552</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>3.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>6553</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>AUDAX</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1279</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>6553</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>AUDAX</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.1337</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>3.0TD</t>
         </is>

--- a/MULTIPUNTO/6553 Datos Multipunto ZUCCHETTI SOFTWARE SPAIN.xlsx
+++ b/MULTIPUNTO/6553 Datos Multipunto ZUCCHETTI SOFTWARE SPAIN.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -427,11 +427,11 @@
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
     <col width="20" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
-    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="21" customWidth="1" min="11" max="11"/>
     <col width="20" customWidth="1" min="12" max="12"/>
     <col width="8" customWidth="1" min="13" max="13"/>
     <col width="8" customWidth="1" min="14" max="14"/>
@@ -1681,6 +1681,238 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>6553</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>NEXUS</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>0.24182</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.163053</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.130629</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>6553</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>NEXUS</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>6553</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>NEXUS</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>0.215785</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.183585</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.14633</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.121653</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.105064</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.125185</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>3.0TD</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>6553</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>NEXUS</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>46212</v>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>46568</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>46213</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>Si</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>3.0TD</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
